--- a/data/trans_orig/P16A01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A01-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29799</t>
+          <t>29953</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29175</t>
+          <t>29185</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27410</t>
+          <t>28117</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53041</t>
+          <t>52831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>243211</t>
+          <t>243057</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>261242</t>
+          <t>260405</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231663</t>
+          <t>231653</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249641</t>
+          <t>249158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>480807</t>
+          <t>481017</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>506438</t>
+          <t>505731</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>21319</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43795</t>
+          <t>44013</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21899</t>
+          <t>21543</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44925</t>
+          <t>43157</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49990</t>
+          <t>47928</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81961</t>
+          <t>78616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>449280</t>
+          <t>449062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>471464</t>
+          <t>471756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>459024</t>
+          <t>460792</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>482050</t>
+          <t>482406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>915063</t>
+          <t>918408</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>947034</t>
+          <t>949096</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23030</t>
+          <t>22822</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13901</t>
+          <t>13331</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32095</t>
+          <t>30412</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295816</t>
+          <t>296024</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310737</t>
+          <t>310779</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321511</t>
+          <t>322081</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332392</t>
+          <t>332540</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622163</t>
+          <t>623846</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640948</t>
+          <t>640894</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30627</t>
+          <t>30502</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12788</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29759</t>
+          <t>29161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30314</t>
+          <t>28352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54843</t>
+          <t>53085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>328044</t>
+          <t>328169</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>345138</t>
+          <t>345370</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>341697</t>
+          <t>342295</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>358668</t>
+          <t>359015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>675284</t>
+          <t>677042</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>699813</t>
+          <t>701775</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22587</t>
+          <t>22713</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23928</t>
+          <t>23144</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20760</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>41211</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180721</t>
+          <t>180595</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194412</t>
+          <t>194837</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183740</t>
+          <t>184524</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199134</t>
+          <t>199535</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369925</t>
+          <t>369765</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>390216</t>
+          <t>390200</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25879</t>
+          <t>25801</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8859</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25136</t>
+          <t>25009</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22719</t>
+          <t>22478</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43995</t>
+          <t>43435</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244932</t>
+          <t>245010</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260381</t>
+          <t>260295</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253008</t>
+          <t>253135</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269119</t>
+          <t>269285</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>504960</t>
+          <t>505520</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>526236</t>
+          <t>526477</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37194</t>
+          <t>36289</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63906</t>
+          <t>63302</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29342</t>
+          <t>28727</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53572</t>
+          <t>53645</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69683</t>
+          <t>70098</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106125</t>
+          <t>106909</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>551121</t>
+          <t>551725</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>577833</t>
+          <t>578738</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>584647</t>
+          <t>584574</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>608877</t>
+          <t>609492</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1147121</t>
+          <t>1146337</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1183563</t>
+          <t>1183148</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49227</t>
+          <t>46880</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77471</t>
+          <t>77090</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54735</t>
+          <t>53779</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87110</t>
+          <t>86238</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>110117</t>
+          <t>108137</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>152616</t>
+          <t>153106</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>665306</t>
+          <t>665687</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>693550</t>
+          <t>695897</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>696401</t>
+          <t>697273</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>728776</t>
+          <t>729732</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1373672</t>
+          <t>1373182</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1416171</t>
+          <t>1418151</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>196981</t>
+          <t>198803</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>255794</t>
+          <t>256265</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>187296</t>
+          <t>189238</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>248215</t>
+          <t>247559</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>405507</t>
+          <t>400407</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>490355</t>
+          <t>487562</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3019731</t>
+          <t>3019260</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3078544</t>
+          <t>3076722</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3130982</t>
+          <t>3131638</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3191901</t>
+          <t>3189959</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6164367</t>
+          <t>6167160</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6249215</t>
+          <t>6254315</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25813</t>
+          <t>26048</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50540</t>
+          <t>50252</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21211</t>
+          <t>22638</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44536</t>
+          <t>45339</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53800</t>
+          <t>53758</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86086</t>
+          <t>85206</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>239663</t>
+          <t>239951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264390</t>
+          <t>264155</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>235807</t>
+          <t>235004</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259132</t>
+          <t>257705</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>484460</t>
+          <t>485340</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>516746</t>
+          <t>516788</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,58%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50191</t>
+          <t>50497</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82039</t>
+          <t>83581</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33030</t>
+          <t>33027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58679</t>
+          <t>57816</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91169</t>
+          <t>90112</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129563</t>
+          <t>132005</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>423488</t>
+          <t>421946</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>455336</t>
+          <t>455030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464052</t>
+          <t>464915</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>489701</t>
+          <t>489704</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>898695</t>
+          <t>896253</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>937089</t>
+          <t>938146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,24%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24794</t>
+          <t>26162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47823</t>
+          <t>48445</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26738</t>
+          <t>25027</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50115</t>
+          <t>48137</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57213</t>
+          <t>56343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90059</t>
+          <t>88125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275293</t>
+          <t>274671</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>298322</t>
+          <t>296954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>290905</t>
+          <t>292883</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>314282</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>574077</t>
+          <t>576011</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>606923</t>
+          <t>607793</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33954</t>
+          <t>36469</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27821</t>
+          <t>26392</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51381</t>
+          <t>51090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45523</t>
+          <t>48009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77273</t>
+          <t>79128</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340028</t>
+          <t>337513</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359044</t>
+          <t>358289</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>336593</t>
+          <t>336884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>360153</t>
+          <t>361582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>684683</t>
+          <t>682828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>716433</t>
+          <t>713947</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17132</t>
+          <t>17335</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37758</t>
+          <t>37500</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13549</t>
+          <t>13853</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32071</t>
+          <t>32435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34036</t>
+          <t>35362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62447</t>
+          <t>62668</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174860</t>
+          <t>175118</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195486</t>
+          <t>195283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187520</t>
+          <t>187156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206042</t>
+          <t>205738</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369762</t>
+          <t>369541</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>398173</t>
+          <t>396847</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30280</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55152</t>
+          <t>54902</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20049</t>
+          <t>19963</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39692</t>
+          <t>41333</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54466</t>
+          <t>54883</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86662</t>
+          <t>86935</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218829</t>
+          <t>219079</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243701</t>
+          <t>243324</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>239448</t>
+          <t>237807</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>259091</t>
+          <t>259177</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>466459</t>
+          <t>466186</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>498655</t>
+          <t>498238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,08%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43054</t>
+          <t>40576</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74583</t>
+          <t>71521</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31905</t>
+          <t>29914</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56604</t>
+          <t>56485</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78884</t>
+          <t>81580</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>120941</t>
+          <t>121843</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>588205</t>
+          <t>591267</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>619734</t>
+          <t>622212</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>637249</t>
+          <t>637368</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>661948</t>
+          <t>663939</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1235700</t>
+          <t>1234798</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1277757</t>
+          <t>1275061</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27181</t>
+          <t>27275</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54729</t>
+          <t>55090</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38685</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66832</t>
+          <t>65410</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72894</t>
+          <t>73650</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>111682</t>
+          <t>113171</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>722243</t>
+          <t>721882</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>749791</t>
+          <t>749697</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>753563</t>
+          <t>754985</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>781710</t>
+          <t>782209</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1485685</t>
+          <t>1484196</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1524473</t>
+          <t>1523717</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>289602</t>
+          <t>286616</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>364737</t>
+          <t>357926</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>265277</t>
+          <t>262955</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>330185</t>
+          <t>336776</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>568021</t>
+          <t>566712</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>667252</t>
+          <t>667732</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3054451</t>
+          <t>3061262</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3129586</t>
+          <t>3132572</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3214862</t>
+          <t>3208271</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3279770</t>
+          <t>3282092</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6296983</t>
+          <t>6296503</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6396214</t>
+          <t>6397523</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>22554</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43916</t>
+          <t>44517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17113</t>
+          <t>17028</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38206</t>
+          <t>35792</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44592</t>
+          <t>44264</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73802</t>
+          <t>72842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249845</t>
+          <t>249244</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272139</t>
+          <t>271207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250497</t>
+          <t>252911</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271590</t>
+          <t>271675</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>508662</t>
+          <t>509622</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>537872</t>
+          <t>538200</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25475</t>
+          <t>25714</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48913</t>
+          <t>49316</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28440</t>
+          <t>28071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53517</t>
+          <t>54670</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59793</t>
+          <t>58888</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93091</t>
+          <t>94486</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>453662</t>
+          <t>453259</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>477100</t>
+          <t>476861</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>469567</t>
+          <t>468414</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>494644</t>
+          <t>495013</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>932568</t>
+          <t>931173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>965866</t>
+          <t>966771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11408</t>
+          <t>11897</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28404</t>
+          <t>28660</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16981</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37826</t>
+          <t>38744</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32176</t>
+          <t>33358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59825</t>
+          <t>60001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>290161</t>
+          <t>289905</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307157</t>
+          <t>306668</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>298483</t>
+          <t>297565</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319666</t>
+          <t>319328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>595049</t>
+          <t>594873</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>622698</t>
+          <t>621516</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>23765</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44550</t>
+          <t>44837</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17476</t>
+          <t>18175</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>37597</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46759</t>
+          <t>46371</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75494</t>
+          <t>75519</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>325414</t>
+          <t>325127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>347442</t>
+          <t>346199</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349076</t>
+          <t>349686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369807</t>
+          <t>369108</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>681753</t>
+          <t>681728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>710488</t>
+          <t>710876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>22543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25837</t>
+          <t>27094</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22519</t>
+          <t>21902</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42408</t>
+          <t>43191</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>189397</t>
+          <t>188678</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203655</t>
+          <t>203637</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>192750</t>
+          <t>191493</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207737</t>
+          <t>207570</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>387400</t>
+          <t>386617</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407289</t>
+          <t>407906</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28998</t>
+          <t>27931</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16346</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35196</t>
+          <t>35955</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31667</t>
+          <t>31978</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57682</t>
+          <t>57012</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234125</t>
+          <t>235192</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251997</t>
+          <t>252358</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237919</t>
+          <t>237160</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256769</t>
+          <t>255592</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>478556</t>
+          <t>479226</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>504571</t>
+          <t>504260</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41568</t>
+          <t>40571</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71348</t>
+          <t>69709</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40016</t>
+          <t>38667</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68083</t>
+          <t>67225</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88614</t>
+          <t>88073</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132174</t>
+          <t>129469</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>585210</t>
+          <t>586849</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>614990</t>
+          <t>615987</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>623211</t>
+          <t>624069</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>651278</t>
+          <t>652627</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1215678</t>
+          <t>1218383</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1259238</t>
+          <t>1259779</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40880</t>
+          <t>41061</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>68788</t>
+          <t>69502</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64348</t>
+          <t>64725</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100813</t>
+          <t>102535</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>113098</t>
+          <t>112746</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>160419</t>
+          <t>159678</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>709795</t>
+          <t>709081</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>737703</t>
+          <t>737522</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>725354</t>
+          <t>723632</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>761819</t>
+          <t>761442</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1444331</t>
+          <t>1445072</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1491652</t>
+          <t>1492004</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>230616</t>
+          <t>229355</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>296394</t>
+          <t>294465</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,82 +10138,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>295278</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>261307</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>330404</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>556411</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>510177</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>605538</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>8,73%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>295278</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>261087</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>328950</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>556411</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>508103</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>600878</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3097956</t>
+          <t>3099885</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3163734</t>
+          <t>3164995</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,82 +10251,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>91,32%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>93,24%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3062</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3249264</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3214138</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3283235</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>90,68%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>92,63%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6044</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6382481</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6333354</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6428715</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>91,98%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>91,27%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>93,21%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3062</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3249264</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3215592</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3283455</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>90,72%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>92,63%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6044</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6382481</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6338014</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6430789</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>91,98%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>91,34%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>16324</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39613</t>
+          <t>38851</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>14024</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27650</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33698</t>
+          <t>32568</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59990</t>
+          <t>62335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271830</t>
+          <t>272592</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295963</t>
+          <t>295119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>262191</t>
+          <t>261985</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275612</t>
+          <t>275611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>541087</t>
+          <t>538742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>567379</t>
+          <t>568509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10502</t>
+          <t>10251</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32125</t>
+          <t>31534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24860</t>
+          <t>24550</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48465</t>
+          <t>47838</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38860</t>
+          <t>39422</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70749</t>
+          <t>71993</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>485268</t>
+          <t>485859</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>506891</t>
+          <t>507142</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464479</t>
+          <t>465106</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>488084</t>
+          <t>488394</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>959588</t>
+          <t>958344</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>991477</t>
+          <t>990915</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14449</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31927</t>
+          <t>30829</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23937</t>
+          <t>24006</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41750</t>
+          <t>43063</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42544</t>
+          <t>42877</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67386</t>
+          <t>67005</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>284123</t>
+          <t>285221</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301601</t>
+          <t>301798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307378</t>
+          <t>306065</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>325191</t>
+          <t>325122</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>597792</t>
+          <t>598173</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>622634</t>
+          <t>622301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15680</t>
+          <t>16083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41630</t>
+          <t>42201</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>16063</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41762</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35056</t>
+          <t>35902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74316</t>
+          <t>75101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>270927</t>
+          <t>270356</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296877</t>
+          <t>296474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>433625</t>
+          <t>434192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>459110</t>
+          <t>459324</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>713628</t>
+          <t>712843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752888</t>
+          <t>752042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>7879</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18985</t>
+          <t>18933</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18052</t>
+          <t>17975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31803</t>
+          <t>31924</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>27755</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46119</t>
+          <t>45979</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159757</t>
+          <t>159809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170749</t>
+          <t>170863</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176853</t>
+          <t>176732</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190604</t>
+          <t>190681</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>341279</t>
+          <t>341419</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>358893</t>
+          <t>359643</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14228</t>
+          <t>15370</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31819</t>
+          <t>31947</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13015</t>
+          <t>13014</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25928</t>
+          <t>27051</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31589</t>
+          <t>30982</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52478</t>
+          <t>52728</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237817</t>
+          <t>237689</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>255408</t>
+          <t>254266</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231128</t>
+          <t>230005</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244041</t>
+          <t>244042</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>474214</t>
+          <t>473964</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>495103</t>
+          <t>495710</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49230</t>
+          <t>48568</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88313</t>
+          <t>87601</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30331</t>
+          <t>29641</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87883</t>
+          <t>88088</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77824</t>
+          <t>83573</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>161854</t>
+          <t>160782</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>535966</t>
+          <t>536678</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>575049</t>
+          <t>575711</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>761382</t>
+          <t>761177</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>818934</t>
+          <t>819624</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1311690</t>
+          <t>1312762</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1395720</t>
+          <t>1389971</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17128</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53551</t>
+          <t>54511</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33654</t>
+          <t>33462</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54787</t>
+          <t>53636</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>48904</t>
+          <t>46765</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>99972</t>
+          <t>98407</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>875169</t>
+          <t>874209</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>911592</t>
+          <t>913893</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>660064</t>
+          <t>661215</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>681197</t>
+          <t>681389</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1543600</t>
+          <t>1545165</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1594668</t>
+          <t>1596807</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>174870</t>
+          <t>175822</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>265333</t>
+          <t>267910</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>211773</t>
+          <t>214202</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>296798</t>
+          <t>295894</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>428685</t>
+          <t>424323</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>549704</t>
+          <t>548369</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3193487</t>
+          <t>3190910</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3283950</t>
+          <t>3282998</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3360123</t>
+          <t>3361027</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3445148</t>
+          <t>3442719</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6566037</t>
+          <t>6567372</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6687056</t>
+          <t>6691418</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A01-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>29544</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29185</t>
+          <t>29904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28117</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52831</t>
+          <t>51542</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>243057</t>
+          <t>243466</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>260405</t>
+          <t>260898</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231653</t>
+          <t>230934</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249158</t>
+          <t>249598</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>481017</t>
+          <t>482306</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>505731</t>
+          <t>506509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21319</t>
+          <t>21407</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44013</t>
+          <t>45762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>22083</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43157</t>
+          <t>43651</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47928</t>
+          <t>50115</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78616</t>
+          <t>81346</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>449062</t>
+          <t>447313</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>471756</t>
+          <t>471668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>460792</t>
+          <t>460298</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>482406</t>
+          <t>481866</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>918408</t>
+          <t>915678</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>949096</t>
+          <t>946909</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22822</t>
+          <t>24054</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13331</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>13177</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30412</t>
+          <t>30885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296024</t>
+          <t>294792</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310779</t>
+          <t>311113</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322081</t>
+          <t>322890</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332540</t>
+          <t>332600</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>623846</t>
+          <t>623373</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640894</t>
+          <t>641081</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30502</t>
+          <t>31013</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12441</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29161</t>
+          <t>29155</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28352</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53085</t>
+          <t>53509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>328169</t>
+          <t>327658</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>345370</t>
+          <t>345557</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>342295</t>
+          <t>342301</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>359015</t>
+          <t>358815</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>677042</t>
+          <t>676618</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>701775</t>
+          <t>700731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>22101</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23144</t>
+          <t>23922</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>20516</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41211</t>
+          <t>41083</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180595</t>
+          <t>181207</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194837</t>
+          <t>194307</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184524</t>
+          <t>183746</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199535</t>
+          <t>199253</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369765</t>
+          <t>369893</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>390200</t>
+          <t>390460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25801</t>
+          <t>25654</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8859</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25009</t>
+          <t>25467</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22478</t>
+          <t>22214</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43435</t>
+          <t>43977</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245010</t>
+          <t>245157</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260295</t>
+          <t>261018</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253135</t>
+          <t>252677</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269285</t>
+          <t>269090</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>505520</t>
+          <t>504978</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>526477</t>
+          <t>526741</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36289</t>
+          <t>36260</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63302</t>
+          <t>63227</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28727</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53645</t>
+          <t>53037</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70098</t>
+          <t>71062</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106909</t>
+          <t>108884</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>551725</t>
+          <t>551800</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>578738</t>
+          <t>578767</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>584574</t>
+          <t>585182</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>609492</t>
+          <t>609605</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1146337</t>
+          <t>1144362</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1183148</t>
+          <t>1182184</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46880</t>
+          <t>47379</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77090</t>
+          <t>75977</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53779</t>
+          <t>53945</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86238</t>
+          <t>87709</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>108137</t>
+          <t>109791</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>153106</t>
+          <t>155760</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>665687</t>
+          <t>666800</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>695897</t>
+          <t>695398</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>697273</t>
+          <t>695802</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>729732</t>
+          <t>729566</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1373182</t>
+          <t>1370528</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1418151</t>
+          <t>1416497</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>198803</t>
+          <t>200192</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>256265</t>
+          <t>258625</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>189238</t>
+          <t>190866</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>247559</t>
+          <t>247570</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>400407</t>
+          <t>405828</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>487562</t>
+          <t>486224</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3019260</t>
+          <t>3016900</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3076722</t>
+          <t>3075333</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3131638</t>
+          <t>3131627</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3189959</t>
+          <t>3188331</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6167160</t>
+          <t>6168498</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6254315</t>
+          <t>6248894</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26048</t>
+          <t>26868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50252</t>
+          <t>50636</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22638</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45339</t>
+          <t>43578</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53758</t>
+          <t>54293</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85206</t>
+          <t>84629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>239951</t>
+          <t>239567</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264155</t>
+          <t>263335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>235004</t>
+          <t>236765</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257705</t>
+          <t>258094</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>485340</t>
+          <t>485917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>516788</t>
+          <t>516253</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50497</t>
+          <t>50975</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83581</t>
+          <t>83776</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33027</t>
+          <t>32886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57816</t>
+          <t>58499</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90112</t>
+          <t>88770</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>132005</t>
+          <t>129764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>421946</t>
+          <t>421751</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>455030</t>
+          <t>454552</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464915</t>
+          <t>464232</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>489704</t>
+          <t>489845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>896253</t>
+          <t>898494</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>938146</t>
+          <t>939488</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26162</t>
+          <t>25114</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48445</t>
+          <t>48181</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25027</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48137</t>
+          <t>50918</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56343</t>
+          <t>56744</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88125</t>
+          <t>89370</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274671</t>
+          <t>274935</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>296954</t>
+          <t>298002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>292883</t>
+          <t>290102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315993</t>
+          <t>315000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>576011</t>
+          <t>574766</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>607793</t>
+          <t>607392</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>15041</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36469</t>
+          <t>36285</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26392</t>
+          <t>27177</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51090</t>
+          <t>51502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48009</t>
+          <t>46294</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79128</t>
+          <t>79926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>337513</t>
+          <t>337697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358289</t>
+          <t>358941</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>336884</t>
+          <t>336472</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361582</t>
+          <t>360797</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>682828</t>
+          <t>682030</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>713947</t>
+          <t>715662</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,92%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17335</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37500</t>
+          <t>38961</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13853</t>
+          <t>13891</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32435</t>
+          <t>31619</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35362</t>
+          <t>34445</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62668</t>
+          <t>61260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175118</t>
+          <t>173657</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195283</t>
+          <t>196280</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187156</t>
+          <t>187972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205738</t>
+          <t>205700</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369541</t>
+          <t>370949</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>396847</t>
+          <t>397764</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>30670</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54902</t>
+          <t>55182</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19963</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41333</t>
+          <t>40170</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54883</t>
+          <t>55096</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86935</t>
+          <t>86439</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219079</t>
+          <t>218799</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243324</t>
+          <t>243311</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237807</t>
+          <t>238970</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>259177</t>
+          <t>259359</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>466186</t>
+          <t>466682</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>498238</t>
+          <t>498025</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40576</t>
+          <t>42780</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71521</t>
+          <t>72507</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29914</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56485</t>
+          <t>57842</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81580</t>
+          <t>79172</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121843</t>
+          <t>118943</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>591267</t>
+          <t>590281</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>622212</t>
+          <t>620008</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>637368</t>
+          <t>636011</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>663939</t>
+          <t>662950</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1234798</t>
+          <t>1237698</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1275061</t>
+          <t>1277469</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27275</t>
+          <t>27849</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55090</t>
+          <t>54325</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38917</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65410</t>
+          <t>66622</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73650</t>
+          <t>73929</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>113171</t>
+          <t>112596</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>721882</t>
+          <t>722647</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>749697</t>
+          <t>749123</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>754985</t>
+          <t>753773</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>782209</t>
+          <t>781478</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1484196</t>
+          <t>1484771</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1523717</t>
+          <t>1523438</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>286616</t>
+          <t>286621</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>357926</t>
+          <t>359400</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>262955</t>
+          <t>258865</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>336776</t>
+          <t>330169</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>566712</t>
+          <t>569144</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>667732</t>
+          <t>671198</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3061262</t>
+          <t>3059788</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3132572</t>
+          <t>3132567</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3208271</t>
+          <t>3214878</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3282092</t>
+          <t>3286182</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6296503</t>
+          <t>6293037</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6397523</t>
+          <t>6395091</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22554</t>
+          <t>22547</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44517</t>
+          <t>43573</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17028</t>
+          <t>17858</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35792</t>
+          <t>37301</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44264</t>
+          <t>45686</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72842</t>
+          <t>73732</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249244</t>
+          <t>250188</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>271207</t>
+          <t>271214</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252911</t>
+          <t>251402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271675</t>
+          <t>270845</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>509622</t>
+          <t>508732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>538200</t>
+          <t>536778</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25714</t>
+          <t>25349</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49316</t>
+          <t>49445</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28071</t>
+          <t>27803</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54670</t>
+          <t>52807</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58888</t>
+          <t>60458</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94486</t>
+          <t>94899</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>453259</t>
+          <t>453130</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>476861</t>
+          <t>477226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>468414</t>
+          <t>470277</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495013</t>
+          <t>495281</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>931173</t>
+          <t>930760</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>966771</t>
+          <t>965201</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11897</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28660</t>
+          <t>29376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,82 +8080,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>25999</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>16012</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>37675</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>7,73%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>44961</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>32124</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>58911</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>9,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>25999</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>16981</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>38744</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,73%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>11,52%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>44961</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>33358</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>60001</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289905</t>
+          <t>289189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>306668</t>
+          <t>306114</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,82 +8193,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>90,78%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,09%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>310310</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>298634</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>320297</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>92,27%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>88,8%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>95,24%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>609913</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>595963</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>622750</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>93,13%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>91,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>310310</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>297565</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>319328</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,27%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>88,48%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>623</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>609913</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>594873</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>621516</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>93,13%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>90,84%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23765</t>
+          <t>23652</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44837</t>
+          <t>46083</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18175</t>
+          <t>18237</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37597</t>
+          <t>38083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46371</t>
+          <t>45064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75519</t>
+          <t>74253</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>325127</t>
+          <t>323881</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>346199</t>
+          <t>346312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349686</t>
+          <t>349200</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369108</t>
+          <t>369046</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>681728</t>
+          <t>682994</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>710876</t>
+          <t>712183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7584</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22543</t>
+          <t>23217</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27094</t>
+          <t>26960</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21902</t>
+          <t>21989</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43191</t>
+          <t>43170</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>188678</t>
+          <t>188004</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203637</t>
+          <t>202931</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191493</t>
+          <t>191627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207570</t>
+          <t>207294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>386638</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407906</t>
+          <t>407819</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27931</t>
+          <t>28439</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17523</t>
+          <t>17270</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35955</t>
+          <t>36101</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31978</t>
+          <t>32453</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57012</t>
+          <t>60386</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235192</t>
+          <t>234684</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252358</t>
+          <t>251820</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237160</t>
+          <t>237014</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>255592</t>
+          <t>255845</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>479226</t>
+          <t>475852</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>504260</t>
+          <t>503785</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40571</t>
+          <t>41063</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69709</t>
+          <t>71569</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38667</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67225</t>
+          <t>68618</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88073</t>
+          <t>90262</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129469</t>
+          <t>135216</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>586849</t>
+          <t>584989</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>615987</t>
+          <t>615495</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>624069</t>
+          <t>622676</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>652627</t>
+          <t>651123</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1218383</t>
+          <t>1212636</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1259779</t>
+          <t>1257590</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41061</t>
+          <t>41557</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69502</t>
+          <t>69553</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64725</t>
+          <t>64787</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>102535</t>
+          <t>103279</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>112746</t>
+          <t>115386</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>159678</t>
+          <t>163481</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>709081</t>
+          <t>709030</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>737522</t>
+          <t>737026</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>723632</t>
+          <t>722888</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>761442</t>
+          <t>761380</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1445072</t>
+          <t>1441269</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1492004</t>
+          <t>1489364</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>229355</t>
+          <t>231227</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>294465</t>
+          <t>294228</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>261307</t>
+          <t>262304</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>330404</t>
+          <t>330691</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>510177</t>
+          <t>513221</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>605538</t>
+          <t>608988</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3099885</t>
+          <t>3100122</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3164995</t>
+          <t>3163123</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3214138</t>
+          <t>3213851</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3283235</t>
+          <t>3282238</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6333354</t>
+          <t>6329904</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6428715</t>
+          <t>6425671</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25768</t>
+          <t>23828</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38851</t>
+          <t>35433</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19943</t>
+          <t>20857</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14024</t>
+          <t>14912</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27650</t>
+          <t>30768</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>45711</t>
+          <t>44686</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32568</t>
+          <t>33709</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62335</t>
+          <t>57204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>285675</t>
+          <t>295017</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>272592</t>
+          <t>283412</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295119</t>
+          <t>303296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>269692</t>
+          <t>295204</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261985</t>
+          <t>285293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275611</t>
+          <t>301149</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>555366</t>
+          <t>590220</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>538742</t>
+          <t>577702</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>568509</t>
+          <t>601197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18907</t>
+          <t>18891</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31534</t>
+          <t>30504</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34343</t>
+          <t>34835</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24550</t>
+          <t>25572</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47838</t>
+          <t>49514</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>53250</t>
+          <t>53726</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39422</t>
+          <t>40675</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71993</t>
+          <t>72310</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>498486</t>
+          <t>510769</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>485859</t>
+          <t>499156</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>507142</t>
+          <t>519109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>478601</t>
+          <t>509613</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>465106</t>
+          <t>494934</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>488394</t>
+          <t>518876</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>977087</t>
+          <t>1020382</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>958344</t>
+          <t>1001798</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>990915</t>
+          <t>1033433</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512944</t>
+          <t>544448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512944</t>
+          <t>544448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512944</t>
+          <t>544448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1030337</t>
+          <t>1074108</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1030337</t>
+          <t>1074108</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1030337</t>
+          <t>1074108</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21494</t>
+          <t>24291</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14252</t>
+          <t>16174</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30829</t>
+          <t>36245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32404</t>
+          <t>34678</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24006</t>
+          <t>26251</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43063</t>
+          <t>44519</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>53898</t>
+          <t>58969</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42877</t>
+          <t>46833</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67005</t>
+          <t>73035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>294556</t>
+          <t>291702</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>285221</t>
+          <t>279748</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301798</t>
+          <t>299819</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>316724</t>
+          <t>321703</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>306065</t>
+          <t>311862</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>325122</t>
+          <t>330130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>611280</t>
+          <t>613406</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>598173</t>
+          <t>599340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>622301</t>
+          <t>625542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26115</t>
+          <t>30218</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16083</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42201</t>
+          <t>47557</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27420</t>
+          <t>30184</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>21186</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41195</t>
+          <t>44402</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>53535</t>
+          <t>60402</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35902</t>
+          <t>43446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75101</t>
+          <t>80716</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>286442</t>
+          <t>342927</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>270356</t>
+          <t>325588</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296474</t>
+          <t>354967</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>447967</t>
+          <t>391446</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>434192</t>
+          <t>377228</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>459324</t>
+          <t>400444</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>734409</t>
+          <t>734373</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>712843</t>
+          <t>714059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752042</t>
+          <t>751329</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12660</t>
+          <t>14304</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7879</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18933</t>
+          <t>21089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23686</t>
+          <t>25240</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17975</t>
+          <t>19125</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31924</t>
+          <t>34505</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>36346</t>
+          <t>39544</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27755</t>
+          <t>31552</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45979</t>
+          <t>49502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>166082</t>
+          <t>191361</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159809</t>
+          <t>184576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170863</t>
+          <t>196941</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>184970</t>
+          <t>201975</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176732</t>
+          <t>192710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190681</t>
+          <t>208090</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>351052</t>
+          <t>393335</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>341419</t>
+          <t>383377</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359643</t>
+          <t>401327</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22118</t>
+          <t>21919</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15370</t>
+          <t>14681</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31947</t>
+          <t>31274</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>13887</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27051</t>
+          <t>26848</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>40787</t>
+          <t>41588</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30982</t>
+          <t>32432</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52728</t>
+          <t>53571</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>247518</t>
+          <t>248788</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237689</t>
+          <t>239433</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>254266</t>
+          <t>256026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>238388</t>
+          <t>244081</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>230005</t>
+          <t>236902</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244042</t>
+          <t>249863</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>485905</t>
+          <t>492869</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>473964</t>
+          <t>480886</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>495710</t>
+          <t>502025</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>65695</t>
+          <t>76935</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48568</t>
+          <t>56888</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87601</t>
+          <t>101193</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>62465</t>
+          <t>74992</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29641</t>
+          <t>60626</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88088</t>
+          <t>92826</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>128160</t>
+          <t>151928</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>83573</t>
+          <t>128705</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>160782</t>
+          <t>180715</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>558584</t>
+          <t>642752</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>536678</t>
+          <t>618494</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>575711</t>
+          <t>662799</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>786800</t>
+          <t>697065</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>761177</t>
+          <t>679231</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>819624</t>
+          <t>711431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1345384</t>
+          <t>1339816</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1312762</t>
+          <t>1311029</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1389971</t>
+          <t>1363039</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>35873</t>
+          <t>43283</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>31865</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54511</t>
+          <t>57992</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>42563</t>
+          <t>47867</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33462</t>
+          <t>37723</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53636</t>
+          <t>60032</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>78436</t>
+          <t>91149</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46765</t>
+          <t>74506</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>98407</t>
+          <t>110131</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>892847</t>
+          <t>754789</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>874209</t>
+          <t>740080</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>913893</t>
+          <t>766207</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>672288</t>
+          <t>782139</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>661215</t>
+          <t>769974</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>681389</t>
+          <t>792283</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1565136</t>
+          <t>1536929</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1545165</t>
+          <t>1517947</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1596807</t>
+          <t>1553572</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>228631</t>
+          <t>253669</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>175822</t>
+          <t>221574</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>267910</t>
+          <t>293991</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>261492</t>
+          <t>288323</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>214202</t>
+          <t>260374</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>295894</t>
+          <t>318892</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>490123</t>
+          <t>541992</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>424323</t>
+          <t>500101</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>548369</t>
+          <t>589879</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>6,89%</t>
         </is>
       </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3230189</t>
+          <t>3278106</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3190910</t>
+          <t>3237784</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3282998</t>
+          <t>3310201</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3395429</t>
+          <t>3443225</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3361027</t>
+          <t>3412656</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3442719</t>
+          <t>3471174</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6625618</t>
+          <t>6721331</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6567372</t>
+          <t>6673444</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6691418</t>
+          <t>6763222</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
+          <t>92,54%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>91,88%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>93,11%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>92,29%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3656921</t>
+          <t>3731548</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3656921</t>
+          <t>3731548</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3656921</t>
+          <t>3731548</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7115741</t>
+          <t>7263323</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7115741</t>
+          <t>7263323</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7115741</t>
+          <t>7263323</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
